--- a/data/trans_dic/P04D$individual-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,92; 35,16</t>
+          <t>26,88; 35,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,71; 32,96</t>
+          <t>24,41; 33,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 25,05</t>
+          <t>10,78; 25,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,91; 32,52</t>
+          <t>23,46; 32,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,84; 36,98</t>
+          <t>27,9; 36,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 24,82</t>
+          <t>12,91; 25,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,33; 32,61</t>
+          <t>26,61; 32,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,29; 33,74</t>
+          <t>27,04; 33,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 23,05</t>
+          <t>13,23; 22,52</t>
         </is>
       </c>
     </row>
@@ -788,32 +788,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,18; 32,37</t>
+          <t>25,42; 32,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,86; 33,2</t>
+          <t>25,39; 33,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,21; 22,67</t>
+          <t>13,05; 23,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,91; 34,0</t>
+          <t>26,33; 33,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,7; 35,13</t>
+          <t>28,01; 35,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 20,42</t>
+          <t>9,63; 20,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,07; 33,38</t>
+          <t>28,06; 33,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,0; 20,35</t>
+          <t>12,61; 20,44</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,62; 34,81</t>
+          <t>27,14; 34,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,97; 34,42</t>
+          <t>26,78; 34,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 21,26</t>
+          <t>13,81; 20,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,95; 36,46</t>
+          <t>29,01; 36,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,81; 38,41</t>
+          <t>30,59; 37,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,54; 20,66</t>
+          <t>12,83; 20,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,16; 34,18</t>
+          <t>29,1; 34,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,69; 34,79</t>
+          <t>29,92; 35,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 19,62</t>
+          <t>14,65; 19,72</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,08; 35,21</t>
+          <t>27,31; 35,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,08; 32,75</t>
+          <t>25,34; 32,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,33; 73,81</t>
+          <t>20,45; 76,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,69; 32,81</t>
+          <t>24,89; 33,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,63; 34,14</t>
+          <t>26,41; 33,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,44; 20,93</t>
+          <t>15,37; 20,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,14; 33,02</t>
+          <t>27,22; 32,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,98; 32,27</t>
+          <t>27,02; 32,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,21; 61,37</t>
+          <t>19,2; 56,39</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,51; 35,63</t>
+          <t>26,1; 35,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,5; 34,71</t>
+          <t>26,01; 34,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,24; 21,41</t>
+          <t>15,4; 22,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,13; 32,6</t>
+          <t>24,15; 32,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,72; 37,06</t>
+          <t>27,82; 36,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,49; 16,96</t>
+          <t>12,54; 17,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,63; 33,06</t>
+          <t>26,3; 32,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,0; 34,25</t>
+          <t>27,97; 34,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,42; 18,49</t>
+          <t>14,68; 18,61</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,91; 34,44</t>
+          <t>23,38; 34,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,44; 31,38</t>
+          <t>21,66; 31,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,16; 21,9</t>
+          <t>15,29; 21,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,56; 33,9</t>
+          <t>23,95; 33,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,87; 32,56</t>
+          <t>22,64; 32,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 16,77</t>
+          <t>3,91; 16,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,04; 32,35</t>
+          <t>25,39; 32,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,88; 30,86</t>
+          <t>23,86; 30,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 17,66</t>
+          <t>6,46; 17,53</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,41; 30,1</t>
+          <t>18,26; 30,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,25; 25,87</t>
+          <t>16,33; 25,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,2; 17,54</t>
+          <t>11,26; 17,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,19; 21,5</t>
+          <t>13,66; 21,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,73; 31,26</t>
+          <t>20,41; 30,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,68</t>
+          <t>10,37; 14,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,38; 23,27</t>
+          <t>16,47; 23,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,05; 27,65</t>
+          <t>20,19; 27,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,26; 14,92</t>
+          <t>11,24; 15,04</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,3; 31,41</t>
+          <t>28,11; 31,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26,91; 30,21</t>
+          <t>27,03; 30,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,81; 42,85</t>
+          <t>17,86; 42,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,82; 29,97</t>
+          <t>26,82; 29,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,27; 32,61</t>
+          <t>29,22; 32,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,5; 16,91</t>
+          <t>12,48; 16,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,9; 30,17</t>
+          <t>27,88; 30,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,57; 30,91</t>
+          <t>28,63; 30,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,37; 30,53</t>
+          <t>16,14; 29,59</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>121752; 159010</t>
+          <t>121597; 160056</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99442; 138272</t>
+          <t>102384; 139803</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42627; 100160</t>
+          <t>43113; 102011</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102417; 139291</t>
+          <t>100485; 137454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>110181; 146333</t>
+          <t>110411; 146317</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39267; 77748</t>
+          <t>40427; 78942</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>231875; 287148</t>
+          <t>234333; 288904</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>222474; 275043</t>
+          <t>220456; 273398</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94978; 164341</t>
+          <t>94362; 160580</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>173034; 222391</t>
+          <t>174644; 221788</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>152706; 196059</t>
+          <t>149904; 195997</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55962; 96027</t>
+          <t>55293; 98370</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164220; 207509</t>
+          <t>160664; 206308</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>156119; 197986</t>
+          <t>157870; 200081</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51719; 104273</t>
+          <t>49152; 105967</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>348074; 413933</t>
+          <t>348118; 413974</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>323896; 385233</t>
+          <t>323792; 385189</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121426; 190067</t>
+          <t>117824; 190949</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>188064; 237024</t>
+          <t>184796; 236222</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>180462; 230295</t>
+          <t>179205; 228281</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73716; 113297</t>
+          <t>73618; 111000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>205483; 258782</t>
+          <t>205906; 256618</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>203781; 254039</t>
+          <t>202351; 251268</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80041; 122127</t>
+          <t>75826; 122850</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>405578; 475294</t>
+          <t>404738; 475742</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>394958; 462867</t>
+          <t>398138; 466782</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>163097; 220612</t>
+          <t>164658; 221655</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>165552; 215228</t>
+          <t>166915; 214815</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>162002; 211588</t>
+          <t>163731; 211950</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>180475; 655235</t>
+          <t>181535; 678412</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>151862; 201808</t>
+          <t>153066; 203566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>172828; 221618</t>
+          <t>171418; 218061</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109758; 148776</t>
+          <t>109287; 148358</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>332886; 404891</t>
+          <t>333757; 401860</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>349435; 417977</t>
+          <t>349993; 415200</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>307171; 981164</t>
+          <t>306928; 901561</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>113863; 153005</t>
+          <t>112080; 152358</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>121885; 165870</t>
+          <t>124312; 164608</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85246; 119757</t>
+          <t>86143; 123026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108037; 145985</t>
+          <t>108148; 147524</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>137717; 184125</t>
+          <t>138212; 182059</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68194; 92630</t>
+          <t>68493; 93467</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>233611; 290049</t>
+          <t>230700; 287850</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>272905; 333854</t>
+          <t>272676; 335001</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159352; 204355</t>
+          <t>162216; 205742</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>70985; 106698</t>
+          <t>72430; 106294</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71687; 104906</t>
+          <t>72431; 105420</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55722; 80469</t>
+          <t>56171; 80625</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83404; 119996</t>
+          <t>84794; 119044</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86391; 123006</t>
+          <t>85541; 124621</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26393; 101803</t>
+          <t>23726; 99735</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>166234; 214736</t>
+          <t>168505; 215875</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>170059; 219759</t>
+          <t>169871; 220169</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59109; 172093</t>
+          <t>62950; 170881</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45831; 74915</t>
+          <t>45438; 75912</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41768; 66479</t>
+          <t>41959; 66090</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31662; 49593</t>
+          <t>31838; 50191</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51288; 83631</t>
+          <t>53115; 83375</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>82936; 125073</t>
+          <t>81661; 122324</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43276; 62429</t>
+          <t>44132; 62104</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>104454; 148441</t>
+          <t>105057; 148881</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>131768; 181675</t>
+          <t>132693; 182267</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79701; 105684</t>
+          <t>79595; 106513</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>967788; 1074169</t>
+          <t>961210; 1074530</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>913455; 1025358</t>
+          <t>917657; 1024029</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>615159; 1480020</t>
+          <t>616833; 1457534</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>953284; 1065229</t>
+          <t>953120; 1056955</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1037651; 1155967</t>
+          <t>1035693; 1148130</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>462986; 626384</t>
+          <t>462330; 621803</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1946023; 2104058</t>
+          <t>1944460; 2096331</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1982149; 2144756</t>
+          <t>1986461; 2142806</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1172093; 2185682</t>
+          <t>1155383; 2117910</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$individual-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,88; 35,39</t>
+          <t>26,09; 35,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,41; 33,33</t>
+          <t>24,11; 33,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 25,51</t>
+          <t>11,7; 25,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,46; 32,1</t>
+          <t>23,7; 32,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,9; 36,97</t>
+          <t>27,88; 36,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 25,2</t>
+          <t>12,32; 23,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,61; 32,81</t>
+          <t>26,32; 32,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,04; 33,54</t>
+          <t>26,96; 33,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,23; 22,52</t>
+          <t>13,45; 21,72</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,42; 32,28</t>
+          <t>25,12; 32,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,39; 33,19</t>
+          <t>25,83; 33,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,05; 23,23</t>
+          <t>12,68; 22,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,33; 33,81</t>
+          <t>26,75; 34,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,01; 35,5</t>
+          <t>27,9; 35,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 20,76</t>
+          <t>13,3; 20,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,83; 31,91</t>
+          <t>26,88; 32,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,06; 33,38</t>
+          <t>27,79; 33,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 20,44</t>
+          <t>14,08; 20,35</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,14; 34,69</t>
+          <t>27,43; 35,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,78; 34,12</t>
+          <t>26,86; 33,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 20,82</t>
+          <t>13,21; 20,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,01; 36,16</t>
+          <t>29,02; 36,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,59; 37,99</t>
+          <t>30,78; 38,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,83; 20,78</t>
+          <t>16,59; 22,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,1; 34,21</t>
+          <t>29,29; 34,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,92; 35,08</t>
+          <t>29,72; 34,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,65; 19,72</t>
+          <t>15,67; 20,04</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,31; 35,14</t>
+          <t>27,39; 35,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,34; 32,81</t>
+          <t>25,42; 32,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,45; 76,42</t>
+          <t>17,63; 24,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,89; 33,1</t>
+          <t>24,86; 32,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,41; 33,6</t>
+          <t>26,74; 34,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,37; 20,87</t>
+          <t>16,5; 21,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,22; 32,77</t>
+          <t>27,16; 32,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,02; 32,06</t>
+          <t>27,3; 32,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,2; 56,39</t>
+          <t>18,05; 21,77</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,1; 35,48</t>
+          <t>26,17; 35,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,01; 34,44</t>
+          <t>25,62; 34,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,4; 22,0</t>
+          <t>15,27; 21,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,15; 32,94</t>
+          <t>24,08; 32,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,82; 36,64</t>
+          <t>27,63; 36,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,54; 17,12</t>
+          <t>12,57; 16,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,3; 32,81</t>
+          <t>26,2; 32,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,97; 34,37</t>
+          <t>28,11; 34,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,68; 18,61</t>
+          <t>14,59; 18,38</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,38; 34,31</t>
+          <t>23,29; 34,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,66; 31,53</t>
+          <t>21,83; 31,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,29; 21,94</t>
+          <t>15,22; 21,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,95; 33,63</t>
+          <t>23,72; 33,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,64; 32,99</t>
+          <t>23,05; 32,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 16,43</t>
+          <t>13,64; 18,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,39; 32,52</t>
+          <t>25,09; 32,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,86; 30,92</t>
+          <t>23,74; 30,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 17,53</t>
+          <t>15,23; 19,31</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,26; 30,5</t>
+          <t>18,27; 30,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,33; 25,72</t>
+          <t>16,55; 25,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,26; 17,75</t>
+          <t>11,16; 17,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,66; 21,43</t>
+          <t>13,22; 21,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,41; 30,57</t>
+          <t>21,08; 31,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,6</t>
+          <t>10,54; 15,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,47; 23,34</t>
+          <t>16,44; 23,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,19; 27,74</t>
+          <t>20,59; 27,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,24; 15,04</t>
+          <t>11,52; 15,37</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,11; 31,42</t>
+          <t>28,16; 31,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,03; 30,17</t>
+          <t>26,99; 30,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,86; 42,2</t>
+          <t>16,47; 19,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,82; 29,74</t>
+          <t>26,77; 29,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,22; 32,39</t>
+          <t>29,4; 32,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,48; 16,79</t>
+          <t>15,55; 17,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,88; 30,06</t>
+          <t>27,96; 30,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,63; 30,88</t>
+          <t>28,61; 30,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,14; 29,59</t>
+          <t>16,35; 18,14</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>69989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56759</t>
+          <t>62098</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>124673</t>
+          <t>132088</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>121597; 160056</t>
+          <t>118013; 158881</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>102384; 139803</t>
+          <t>101145; 142030</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43113; 102011</t>
+          <t>47327; 101536</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100485; 137454</t>
+          <t>101496; 137877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>110411; 146317</t>
+          <t>110354; 145957</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40427; 78942</t>
+          <t>44658; 85123</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>234333; 288904</t>
+          <t>231747; 287126</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>220456; 273398</t>
+          <t>219812; 275106</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94362; 160580</t>
+          <t>103190; 166598</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75742</t>
+          <t>80322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82126</t>
+          <t>84620</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>157868</t>
+          <t>164943</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>174644; 221788</t>
+          <t>172617; 222411</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>149904; 195997</t>
+          <t>152497; 196160</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55293; 98370</t>
+          <t>60478; 105033</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160664; 206308</t>
+          <t>163239; 208765</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>157870; 200081</t>
+          <t>157224; 201432</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49152; 105967</t>
+          <t>66503; 103434</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>348118; 413974</t>
+          <t>348759; 416562</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>323792; 385189</t>
+          <t>320742; 384146</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>117824; 190949</t>
+          <t>137571; 198767</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92221</t>
+          <t>102589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>103672</t>
+          <t>118093</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>195893</t>
+          <t>220682</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>184796; 236222</t>
+          <t>186776; 238813</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>179205; 228281</t>
+          <t>179751; 227016</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73618; 111000</t>
+          <t>81433; 123510</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>205906; 256618</t>
+          <t>205965; 256492</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>202351; 251268</t>
+          <t>203551; 251923</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75826; 122850</t>
+          <t>103120; 138341</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>404738; 475742</t>
+          <t>407354; 479082</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>398138; 466782</t>
+          <t>395420; 462316</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164658; 221655</t>
+          <t>193909; 248063</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>382598</t>
+          <t>145659</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>130006</t>
+          <t>137976</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>512604</t>
+          <t>283636</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>166915; 214815</t>
+          <t>167429; 216938</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>163731; 211950</t>
+          <t>164218; 211200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>181535; 678412</t>
+          <t>123513; 168196</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>153066; 203566</t>
+          <t>152918; 200219</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>171418; 218061</t>
+          <t>173595; 220955</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109287; 148358</t>
+          <t>121233; 155892</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>333757; 401860</t>
+          <t>333133; 400967</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>349993; 415200</t>
+          <t>353630; 416233</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>306928; 901561</t>
+          <t>259041; 312526</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103379</t>
+          <t>110550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79714</t>
+          <t>88244</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>183093</t>
+          <t>198794</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>112080; 152358</t>
+          <t>112368; 153642</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>124312; 164608</t>
+          <t>122448; 165814</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86143; 123026</t>
+          <t>92765; 129469</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108148; 147524</t>
+          <t>107847; 146835</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>138212; 182059</t>
+          <t>137258; 183670</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68493; 93467</t>
+          <t>76252; 102686</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>230700; 287850</t>
+          <t>229806; 287386</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>272676; 335001</t>
+          <t>274049; 332078</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162216; 205742</t>
+          <t>177134; 223218</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67650</t>
+          <t>74741</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63085</t>
+          <t>69814</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>130734</t>
+          <t>144556</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>72430; 106294</t>
+          <t>72143; 107091</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72431; 105420</t>
+          <t>72998; 105672</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56171; 80625</t>
+          <t>61809; 88326</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84794; 119044</t>
+          <t>83971; 119776</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>85541; 124621</t>
+          <t>87069; 122912</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23726; 99735</t>
+          <t>59755; 81142</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>168505; 215875</t>
+          <t>166574; 214411</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>169871; 220169</t>
+          <t>169061; 218712</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62950; 170881</t>
+          <t>128548; 163041</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40204</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52577</t>
+          <t>59179</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>92781</t>
+          <t>103519</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45438; 75912</t>
+          <t>45476; 74929</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41959; 66090</t>
+          <t>42521; 66200</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31838; 50191</t>
+          <t>34610; 55811</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53115; 83375</t>
+          <t>51439; 84090</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>81661; 122324</t>
+          <t>84349; 124735</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44132; 62104</t>
+          <t>48918; 70502</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>105057; 148881</t>
+          <t>104889; 147244</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>132693; 182267</t>
+          <t>135292; 183338</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79595; 106513</t>
+          <t>89235; 119015</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>829707</t>
+          <t>628191</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>567939</t>
+          <t>620026</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1397646</t>
+          <t>1248217</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>961210; 1074530</t>
+          <t>962831; 1073187</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>917657; 1024029</t>
+          <t>916057; 1026634</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>616833; 1457534</t>
+          <t>580015; 684328</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>953120; 1056955</t>
+          <t>951445; 1055961</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1035693; 1148130</t>
+          <t>1041940; 1158477</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>462330; 621803</t>
+          <t>579647; 664506</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1944460; 2096331</t>
+          <t>1950028; 2105918</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1986461; 2142806</t>
+          <t>1984874; 2142094</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1155383; 2117910</t>
+          <t>1185152; 1315414</t>
         </is>
       </c>
     </row>
